--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>13.36672707525572</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>13.50266770030553</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>10.93637388532298</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>18.79625957207136</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>14.33753884400248</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>15.08869885242905</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>15.94287850666951</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>17.13323778360692</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>17.60294518680119</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,9 +571,6 @@
       <c r="E11">
         <v>12.35912528794889</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -625,9 +590,6 @@
       <c r="E12">
         <v>12.79292814122255</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -647,9 +609,6 @@
       <c r="E13">
         <v>13.13432031576254</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -669,9 +628,6 @@
       <c r="E14">
         <v>13.12787273277736</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -691,9 +647,6 @@
       <c r="E15">
         <v>12.84716320142618</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -713,9 +666,6 @@
       <c r="E16">
         <v>12.32485714285714</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -735,9 +685,6 @@
       <c r="E17">
         <v>13.02545454545454</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -757,9 +704,6 @@
       <c r="E18">
         <v>12.93730909090909</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -779,9 +723,6 @@
       <c r="E19">
         <v>12.6156710447848</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -801,9 +742,6 @@
       <c r="E20">
         <v>17.57430255880386</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -823,9 +761,6 @@
       <c r="E21">
         <v>9.757711941684978</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -845,9 +780,6 @@
       <c r="E22">
         <v>14.63905288383391</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -867,9 +799,6 @@
       <c r="E23">
         <v>12.27831475035193</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -889,9 +818,6 @@
       <c r="E24">
         <v>15.01973599800752</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -911,9 +837,6 @@
       <c r="E25">
         <v>13.54353011329756</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -933,9 +856,6 @@
       <c r="E26">
         <v>14.5683180944429</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -955,9 +875,6 @@
       <c r="E27">
         <v>12.78554752136365</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -977,9 +894,6 @@
       <c r="E28">
         <v>13.78977820636451</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -999,9 +913,6 @@
       <c r="E29">
         <v>13.60502826080243</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1021,9 +932,6 @@
       <c r="E30">
         <v>17.31262544234398</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1043,9 +951,6 @@
       <c r="E31">
         <v>16.64579649267461</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1065,9 +970,6 @@
       <c r="E32">
         <v>12.25050990103678</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1087,9 +989,6 @@
       <c r="E33">
         <v>14.26080000000001</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1109,9 +1008,6 @@
       <c r="E34">
         <v>11.71960396039604</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1131,9 +1027,6 @@
       <c r="E35">
         <v>14.11837438583932</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1153,9 +1046,6 @@
       <c r="E36">
         <v>13.121392249191</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1175,9 +1065,6 @@
       <c r="E37">
         <v>13.2355</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1197,9 +1084,6 @@
       <c r="E38">
         <v>12.51074999999999</v>
       </c>
-      <c r="F38" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1218,9 +1102,6 @@
       </c>
       <c r="E39">
         <v>14.49361244711491</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -442,7 +442,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Juan Fernandez</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="B5">
@@ -651,456 +651,475 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B16">
-        <v>786274</v>
+        <v>794428</v>
       </c>
       <c r="C16">
         <v>700000</v>
       </c>
       <c r="D16">
-        <v>86274</v>
+        <v>94428</v>
       </c>
       <c r="E16">
-        <v>12.32485714285714</v>
+        <v>13.48971428571428</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="B17">
-        <v>777050</v>
+        <v>786274</v>
       </c>
       <c r="C17">
-        <v>687500</v>
+        <v>700000</v>
       </c>
       <c r="D17">
-        <v>89550</v>
+        <v>86274</v>
       </c>
       <c r="E17">
-        <v>13.02545454545454</v>
+        <v>12.32485714285714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="B18">
-        <v>776444</v>
+        <v>777050</v>
       </c>
       <c r="C18">
         <v>687500</v>
       </c>
       <c r="D18">
-        <v>88944</v>
+        <v>89550</v>
       </c>
       <c r="E18">
-        <v>12.93730909090909</v>
+        <v>13.02545454545454</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="B19">
-        <v>774244</v>
+        <v>776444</v>
       </c>
       <c r="C19">
-        <v>687510</v>
+        <v>687500</v>
       </c>
       <c r="D19">
-        <v>86734</v>
+        <v>88944</v>
       </c>
       <c r="E19">
-        <v>12.6156710447848</v>
+        <v>12.93730909090909</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="B20">
-        <v>773780</v>
+        <v>774244</v>
       </c>
       <c r="C20">
-        <v>658120</v>
+        <v>687510</v>
       </c>
       <c r="D20">
-        <v>115660</v>
+        <v>86734</v>
       </c>
       <c r="E20">
-        <v>17.57430255880386</v>
+        <v>12.6156710447848</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="B21">
-        <v>772736</v>
+        <v>773780</v>
       </c>
       <c r="C21">
-        <v>704038</v>
+        <v>658120</v>
       </c>
       <c r="D21">
-        <v>68698</v>
+        <v>115660</v>
       </c>
       <c r="E21">
-        <v>9.757711941684978</v>
+        <v>17.57430255880386</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="B22">
-        <v>768750</v>
+        <v>772736</v>
       </c>
       <c r="C22">
-        <v>670583</v>
+        <v>704038</v>
       </c>
       <c r="D22">
-        <v>98167</v>
+        <v>68698</v>
       </c>
       <c r="E22">
-        <v>14.63905288383391</v>
+        <v>9.757711941684978</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="B23">
-        <v>762500</v>
+        <v>768750</v>
       </c>
       <c r="C23">
-        <v>679116</v>
+        <v>670583</v>
       </c>
       <c r="D23">
-        <v>83384</v>
+        <v>98167</v>
       </c>
       <c r="E23">
-        <v>12.27831475035193</v>
+        <v>14.63905288383391</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="B24">
-        <v>762000</v>
+        <v>762500</v>
       </c>
       <c r="C24">
-        <v>662495</v>
+        <v>679116</v>
       </c>
       <c r="D24">
-        <v>99505</v>
+        <v>83384</v>
       </c>
       <c r="E24">
-        <v>15.01973599800752</v>
+        <v>12.27831475035193</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="B25">
-        <v>761650</v>
+        <v>762000</v>
       </c>
       <c r="C25">
-        <v>670800</v>
+        <v>662495</v>
       </c>
       <c r="D25">
-        <v>90850</v>
+        <v>99505</v>
       </c>
       <c r="E25">
-        <v>13.54353011329756</v>
+        <v>15.01973599800752</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B26">
-        <v>749184</v>
+        <v>761650</v>
       </c>
       <c r="C26">
-        <v>653919</v>
+        <v>670800</v>
       </c>
       <c r="D26">
-        <v>95265</v>
+        <v>90850</v>
       </c>
       <c r="E26">
-        <v>14.5683180944429</v>
+        <v>13.54353011329756</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="B27">
-        <v>746364</v>
+        <v>749184</v>
       </c>
       <c r="C27">
-        <v>661755</v>
+        <v>653919</v>
       </c>
       <c r="D27">
-        <v>84609</v>
+        <v>95265</v>
       </c>
       <c r="E27">
-        <v>12.78554752136365</v>
+        <v>14.5683180944429</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="B28">
-        <v>737500</v>
+        <v>746364</v>
       </c>
       <c r="C28">
-        <v>648125</v>
+        <v>661755</v>
       </c>
       <c r="D28">
-        <v>89375</v>
+        <v>84609</v>
       </c>
       <c r="E28">
-        <v>13.78977820636451</v>
+        <v>12.78554752136365</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="B29">
-        <v>735638</v>
+        <v>737500</v>
       </c>
       <c r="C29">
-        <v>647540</v>
+        <v>648125</v>
       </c>
       <c r="D29">
-        <v>88098</v>
+        <v>89375</v>
       </c>
       <c r="E29">
-        <v>13.60502826080243</v>
+        <v>13.78977820636451</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="B30">
-        <v>723020</v>
+        <v>735638</v>
       </c>
       <c r="C30">
-        <v>616319</v>
+        <v>647540</v>
       </c>
       <c r="D30">
-        <v>106701</v>
+        <v>88098</v>
       </c>
       <c r="E30">
-        <v>17.31262544234398</v>
+        <v>13.60502826080243</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="B31">
-        <v>718667</v>
+        <v>723020</v>
       </c>
       <c r="C31">
-        <v>616110.5</v>
+        <v>616319</v>
       </c>
       <c r="D31">
-        <v>102556.5</v>
+        <v>106701</v>
       </c>
       <c r="E31">
-        <v>16.64579649267461</v>
+        <v>17.31262544234398</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="B32">
-        <v>714360</v>
+        <v>718667</v>
       </c>
       <c r="C32">
-        <v>636398</v>
+        <v>616110.5</v>
       </c>
       <c r="D32">
-        <v>77962</v>
+        <v>102556.5</v>
       </c>
       <c r="E32">
-        <v>12.25050990103678</v>
+        <v>16.64579649267461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="B33">
-        <v>714130</v>
+        <v>714360</v>
       </c>
       <c r="C33">
-        <v>625000</v>
+        <v>636398</v>
       </c>
       <c r="D33">
-        <v>89130</v>
+        <v>77962</v>
       </c>
       <c r="E33">
-        <v>14.26080000000001</v>
+        <v>12.25050990103678</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="B34">
-        <v>705230</v>
+        <v>714130</v>
       </c>
       <c r="C34">
-        <v>631250</v>
+        <v>625000</v>
       </c>
       <c r="D34">
-        <v>73980</v>
+        <v>89130</v>
       </c>
       <c r="E34">
-        <v>11.71960396039604</v>
+        <v>14.26080000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="B35">
-        <v>701440</v>
+        <v>705230</v>
       </c>
       <c r="C35">
-        <v>614660</v>
+        <v>631250</v>
       </c>
       <c r="D35">
-        <v>86780</v>
+        <v>73980</v>
       </c>
       <c r="E35">
-        <v>14.11837438583932</v>
+        <v>11.71960396039604</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="B36">
-        <v>691282</v>
+        <v>701440</v>
       </c>
       <c r="C36">
-        <v>611097.5</v>
+        <v>614660</v>
       </c>
       <c r="D36">
-        <v>80184.5</v>
+        <v>86780</v>
       </c>
       <c r="E36">
-        <v>13.121392249191</v>
+        <v>14.11837438583932</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="B37">
-        <v>679413</v>
+        <v>691282</v>
       </c>
       <c r="C37">
-        <v>600000</v>
+        <v>611097.5</v>
       </c>
       <c r="D37">
-        <v>79413</v>
+        <v>80184.5</v>
       </c>
       <c r="E37">
-        <v>13.2355</v>
+        <v>13.121392249191</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="B38">
-        <v>675064.5</v>
+        <v>679413</v>
       </c>
       <c r="C38">
         <v>600000</v>
       </c>
       <c r="D38">
-        <v>75064.5</v>
+        <v>79413</v>
       </c>
       <c r="E38">
-        <v>12.51074999999999</v>
+        <v>13.2355</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>El Quisco</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>675064.5</v>
+      </c>
+      <c r="C39">
+        <v>600000</v>
+      </c>
+      <c r="D39">
+        <v>75064.5</v>
+      </c>
+      <c r="E39">
+        <v>12.51074999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Olmué</t>
         </is>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>664640</v>
       </c>
-      <c r="C39">
+      <c r="C40">
         <v>580504</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>84136</v>
       </c>
-      <c r="E39">
+      <c r="E40">
         <v>14.49361244711491</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2023_valparaiso.xlsx
@@ -1130,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1139,20 +1139,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>777050</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1161,48 +1153,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>749184</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>776444</v>
+          <t>Petorca</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>866294</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>691282</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>774244</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1211,148 +1188,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>772736</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1078770</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>675064.5</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>773780</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>737500</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>982046.5</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>679413</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>701440</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>840860</v>
+          <t>El Quisco</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>919845.5</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>860890</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>664640</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>714360</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>705230</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>723020</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1361,148 +1293,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>735638</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>718667</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>768750</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>839830</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>786274</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>862500</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>746364</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>868331</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>762000</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>714130</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>913131</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>761650</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>816579</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>822055</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>762500</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
